--- a/Results/Two_Datasets_Assessment/Cancer/Processed_Data/generator_ranking.xlsx
+++ b/Results/Two_Datasets_Assessment/Cancer/Processed_Data/generator_ranking.xlsx
@@ -485,22 +485,22 @@
         <v>0.968362898094103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2648177399141864</v>
+        <v>0.4849657455036203</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7458789484729241</v>
+        <v>0.7279601106252133</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6905541657537744</v>
+        <v>0.7512229160762912</v>
       </c>
       <c r="F2" t="n">
         <v>0.02533261560431084</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3973204760397929</v>
+        <v>0.4728531538294638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4306859916848103</v>
+        <v>0.3868807022146142</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -509,29 +509,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8534899925686222</v>
+        <v>0.9355254935904923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5133862651733053</v>
+        <v>0.4785157516103453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5363147907251201</v>
+        <v>0.7262959665789475</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6563063137969766</v>
+        <v>0.7356537128929848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03844262538306072</v>
+        <v>0.03091233954307604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4190367853106954</v>
+        <v>0.4815889446704471</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4520312730149757</v>
+        <v>0.3734551008039336</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -540,29 +540,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9230599709384475</v>
+        <v>0.8200940787089187</v>
       </c>
       <c r="C4" t="n">
-        <v>0.413774075177361</v>
+        <v>0.519908292713704</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4877173849809624</v>
+        <v>0.8121587739421542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.639671426422876</v>
+        <v>0.7276577514803249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0299390574391596</v>
+        <v>0.04558184888203832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4362112587722336</v>
+        <v>0.4595556126630457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4592444829575035</v>
+        <v>0.344598893877038</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -571,29 +571,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8200940787089187</v>
+        <v>0.9230599709384475</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3928241452145236</v>
+        <v>0.5372078162303315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6147824256659962</v>
+        <v>0.5817496483258702</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6303196027477234</v>
+        <v>0.7049112277422396</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04558184888203832</v>
+        <v>0.0299390574391596</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4460124703686378</v>
+        <v>0.4465408135061384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3948195200317383</v>
+        <v>0.3266270920749452</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -602,29 +602,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9355254935904923</v>
+        <v>0.8534899925686222</v>
       </c>
       <c r="C6" t="n">
-        <v>0.255724578002569</v>
+        <v>0.5275669612932169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5695028378343651</v>
+        <v>0.6670557325674165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6217784221872772</v>
+        <v>0.699782805185639</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03091233954307604</v>
+        <v>0.03844262538306072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.407271732796022</v>
+        <v>0.3925352606417877</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4284281443663037</v>
+        <v>0.3020752481436006</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -640,22 +640,22 @@
         <v>0.7038964675556111</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4750360720991947</v>
+        <v>0.4872794696822143</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3123008246014149</v>
+        <v>0.2013340430684206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5177596560324272</v>
+        <v>0.4881426408474349</v>
       </c>
       <c r="F7" t="n">
         <v>0.04208972191513813</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3313262612729288</v>
+        <v>0.2798978131734407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3977363801222663</v>
+        <v>0.2911875017735279</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -671,22 +671,22 @@
         <v>0.3220413157082996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5143939653183046</v>
+        <v>0.4629545687864741</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4597927818721145</v>
+        <v>0.7201306164880913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4210725504404456</v>
+        <v>0.4837420818656895</v>
       </c>
       <c r="F8" t="n">
         <v>0.1586658384894548</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4731592883193763</v>
+        <v>0.4746639280065832</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4618239786791074</v>
+        <v>0.3716551046688774</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -702,22 +702,22 @@
         <v>0.3729653880480129</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3682877872336551</v>
+        <v>0.493020634446126</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3801171918778428</v>
+        <v>0.1717370163302168</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3737076489526545</v>
+        <v>0.348613450452108</v>
       </c>
       <c r="F9" t="n">
         <v>0.07790029599774173</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2472718850136229</v>
+        <v>0.2113072186826778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3416095923426357</v>
+        <v>0.2943798743041575</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
